--- a/data/trans_orig/P16A_n_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35191</t>
+          <t>35510</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58753</t>
+          <t>60669</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56068</t>
+          <t>55656</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85573</t>
+          <t>84958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97887</t>
+          <t>98029</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137523</t>
+          <t>137170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>214257</t>
+          <t>212341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237819</t>
+          <t>237500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175265</t>
+          <t>175880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>204770</t>
+          <t>205182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396325</t>
+          <t>396678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435961</t>
+          <t>435819</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53837</t>
+          <t>54605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84359</t>
+          <t>86071</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135191</t>
+          <t>134970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176056</t>
+          <t>176320</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198980</t>
+          <t>198194</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250769</t>
+          <t>250393</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>408716</t>
+          <t>407004</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>439238</t>
+          <t>438470</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327893</t>
+          <t>327629</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368758</t>
+          <t>368979</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>746255</t>
+          <t>746631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798044</t>
+          <t>798830</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,04%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39340</t>
+          <t>40008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65060</t>
+          <t>65998</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72449</t>
+          <t>73710</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104038</t>
+          <t>105162</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>120633</t>
+          <t>118687</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>162969</t>
+          <t>160042</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>253786</t>
+          <t>252848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279506</t>
+          <t>278838</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>231374</t>
+          <t>230250</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>262963</t>
+          <t>261702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>491289</t>
+          <t>494216</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>533625</t>
+          <t>535571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,86%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50624</t>
+          <t>52487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>79115</t>
+          <t>81051</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>103127</t>
+          <t>102388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137091</t>
+          <t>139040</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160206</t>
+          <t>160448</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>204179</t>
+          <t>205978</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>279556</t>
+          <t>277620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308047</t>
+          <t>306184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234365</t>
+          <t>232416</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268329</t>
+          <t>269068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>72,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>525948</t>
+          <t>524149</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569921</t>
+          <t>569679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>22002</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43999</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60806</t>
+          <t>59304</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>89762</t>
+          <t>87821</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>89444</t>
+          <t>87707</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127549</t>
+          <t>123098</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>159309</t>
+          <t>160197</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180298</t>
+          <t>181306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117906</t>
+          <t>119847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>146862</t>
+          <t>148364</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>283427</t>
+          <t>287878</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321532</t>
+          <t>323269</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37711</t>
+          <t>37873</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61082</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68537</t>
+          <t>67112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>99096</t>
+          <t>96389</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112461</t>
+          <t>112202</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150644</t>
+          <t>150314</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209729</t>
+          <t>209294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>233100</t>
+          <t>232938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179048</t>
+          <t>181755</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209607</t>
+          <t>211032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398311</t>
+          <t>398641</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436494</t>
+          <t>436753</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,56%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89735</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>127842</t>
+          <t>125541</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158760</t>
+          <t>159228</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>207556</t>
+          <t>204007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>259116</t>
+          <t>260314</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>319157</t>
+          <t>317865</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>487185</t>
+          <t>489486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>525292</t>
+          <t>525730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>430663</t>
+          <t>434212</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>479459</t>
+          <t>478991</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>934089</t>
+          <t>935381</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>994130</t>
+          <t>992932</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133727</t>
+          <t>133282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177007</t>
+          <t>177286</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>212099</t>
+          <t>210750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>266391</t>
+          <t>261217</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>357950</t>
+          <t>359280</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>425788</t>
+          <t>426686</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>566788</t>
+          <t>566509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610068</t>
+          <t>610513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>517120</t>
+          <t>522294</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>571412</t>
+          <t>572761</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>73,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1101518</t>
+          <t>1100620</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1169356</t>
+          <t>1168026</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,48%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>528509</t>
+          <t>528764</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>612482</t>
+          <t>612259</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>951145</t>
+          <t>957519</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1064005</t>
+          <t>1062880</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1510894</t>
+          <t>1508901</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1648760</t>
+          <t>1646994</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2664061</t>
+          <t>2664284</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2748034</t>
+          <t>2747779</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2315192</t>
+          <t>2316317</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2428052</t>
+          <t>2421678</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5006981</t>
+          <t>5008747</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5144847</t>
+          <t>5146840</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,33%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>57710</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88471</t>
+          <t>88762</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>100937</t>
+          <t>102530</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137295</t>
+          <t>138057</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167192</t>
+          <t>170189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215561</t>
+          <t>216288</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>206267</t>
+          <t>205976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238834</t>
+          <t>237028</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149950</t>
+          <t>149188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186308</t>
+          <t>184715</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>366422</t>
+          <t>365695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>414791</t>
+          <t>411794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>70,76%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111687</t>
+          <t>112439</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154952</t>
+          <t>153868</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>196487</t>
+          <t>195487</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>239969</t>
+          <t>243780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>316741</t>
+          <t>318099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>382732</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>37,23%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350575</t>
+          <t>351659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393840</t>
+          <t>393088</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283796</t>
+          <t>279985</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>327278</t>
+          <t>328278</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>53,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646560</t>
+          <t>646041</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>712551</t>
+          <t>711193</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,1%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79888</t>
+          <t>79695</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113510</t>
+          <t>113806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129977</t>
+          <t>131386</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167998</t>
+          <t>168859</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220855</t>
+          <t>221309</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>270115</t>
+          <t>273219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>41,08%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210536</t>
+          <t>210240</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244158</t>
+          <t>244351</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>173022</t>
+          <t>172161</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211043</t>
+          <t>209634</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>394951</t>
+          <t>391847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444211</t>
+          <t>443757</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>58,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75906</t>
+          <t>74759</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111400</t>
+          <t>110778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157356</t>
+          <t>156856</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>197586</t>
+          <t>195268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>241005</t>
+          <t>243474</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297842</t>
+          <t>297448</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>262582</t>
+          <t>263204</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298076</t>
+          <t>299223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>80,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191365</t>
+          <t>193683</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231595</t>
+          <t>232095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465091</t>
+          <t>465485</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>521928</t>
+          <t>519459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46279</t>
+          <t>46484</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73383</t>
+          <t>73341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102153</t>
+          <t>103758</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>131423</t>
+          <t>133287</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,52%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>60,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156400</t>
+          <t>156469</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197955</t>
+          <t>196858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,55%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139235</t>
+          <t>139277</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166339</t>
+          <t>166134</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88168</t>
+          <t>86304</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>117438</t>
+          <t>115833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>234254</t>
+          <t>235351</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275809</t>
+          <t>275740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73380</t>
+          <t>73833</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>103360</t>
+          <t>105655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>104462</t>
+          <t>106444</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>139956</t>
+          <t>140625</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>187162</t>
+          <t>190139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234816</t>
+          <t>234525</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,33%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>170621</t>
+          <t>168326</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200601</t>
+          <t>200148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>140075</t>
+          <t>139406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>175569</t>
+          <t>173587</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319196</t>
+          <t>319487</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>366850</t>
+          <t>363873</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>139410</t>
+          <t>135533</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>185343</t>
+          <t>183807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>237724</t>
+          <t>238438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>291103</t>
+          <t>287912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388981</t>
+          <t>388431</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>461223</t>
+          <t>459692</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,88%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>477445</t>
+          <t>478981</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>523378</t>
+          <t>527255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>402750</t>
+          <t>405941</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>456129</t>
+          <t>455415</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>895418</t>
+          <t>896949</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>967660</t>
+          <t>968210</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>144127</t>
+          <t>142913</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>191620</t>
+          <t>188713</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>230091</t>
+          <t>229313</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>284950</t>
+          <t>284878</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>388325</t>
+          <t>384904</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>461686</t>
+          <t>459734</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>587478</t>
+          <t>590385</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>634971</t>
+          <t>636185</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>538903</t>
+          <t>538975</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>593762</t>
+          <t>594540</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1141265</t>
+          <t>1143217</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1214626</t>
+          <t>1218047</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>75,77%</t>
+          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>815615</t>
+          <t>813379</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>920105</t>
+          <t>919139</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1365655</t>
+          <t>1364502</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1482575</t>
+          <t>1482274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2210371</t>
+          <t>2212676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2375709</t>
+          <t>2370765</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,94%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2506674</t>
+          <t>2507640</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2611164</t>
+          <t>2613400</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2075734</t>
+          <t>2076035</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2192654</t>
+          <t>2193807</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4609379</t>
+          <t>4614323</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4774717</t>
+          <t>4772412</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,32%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42587</t>
+          <t>41414</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>70737</t>
+          <t>68530</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72426</t>
+          <t>73947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105336</t>
+          <t>105579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>125307</t>
+          <t>124322</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>168559</t>
+          <t>165007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,33%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>223024</t>
+          <t>225231</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>251174</t>
+          <t>252347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183367</t>
+          <t>183124</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>216277</t>
+          <t>214756</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>413905</t>
+          <t>417457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>457157</t>
+          <t>458142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,49%</t>
+          <t>78,66%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>97084</t>
+          <t>98304</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135960</t>
+          <t>136170</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>175596</t>
+          <t>174659</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219715</t>
+          <t>219201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,57%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279846</t>
+          <t>281382</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>337857</t>
+          <t>339341</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366615</t>
+          <t>366405</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>405491</t>
+          <t>404271</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303369</t>
+          <t>303883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347488</t>
+          <t>348425</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>687802</t>
+          <t>686318</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745813</t>
+          <t>744277</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>72,57%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55459</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>83921</t>
+          <t>84064</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79777</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>113826</t>
+          <t>114700</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146325</t>
+          <t>146744</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>187939</t>
+          <t>190489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>29,09%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234644</t>
+          <t>234501</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>263106</t>
+          <t>262717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>222483</t>
+          <t>221609</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>256532</t>
+          <t>255420</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>466935</t>
+          <t>464385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>508549</t>
+          <t>508130</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>70,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93764</t>
+          <t>92431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129518</t>
+          <t>130630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150593</t>
+          <t>150219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192482</t>
+          <t>190666</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254250</t>
+          <t>253861</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>308515</t>
+          <t>312351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,25%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>240446</t>
+          <t>239334</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>276200</t>
+          <t>277533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194801</t>
+          <t>196617</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>236690</t>
+          <t>237064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>448732</t>
+          <t>444896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>502997</t>
+          <t>503386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,26%</t>
+          <t>58,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30959</t>
+          <t>30342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53746</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82903</t>
+          <t>83667</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110421</t>
+          <t>113156</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121302</t>
+          <t>120138</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157356</t>
+          <t>158384</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,85%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157722</t>
+          <t>157475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180262</t>
+          <t>180879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>108166</t>
+          <t>105431</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>135684</t>
+          <t>134920</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>272452</t>
+          <t>271424</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>308506</t>
+          <t>309670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42041</t>
+          <t>41345</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67569</t>
+          <t>68746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>69585</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100800</t>
+          <t>98562</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118788</t>
+          <t>119284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160372</t>
+          <t>160514</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,93%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195554</t>
+          <t>194377</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221082</t>
+          <t>221778</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>172315</t>
+          <t>174553</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205380</t>
+          <t>203530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375866</t>
+          <t>375724</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>417450</t>
+          <t>416954</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,76%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117996</t>
+          <t>117014</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>162959</t>
+          <t>160210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>183120</t>
+          <t>185164</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232030</t>
+          <t>232918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>317074</t>
+          <t>317042</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>380895</t>
+          <t>381361</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>493599</t>
+          <t>496348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>538562</t>
+          <t>539544</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>459264</t>
+          <t>458376</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>508174</t>
+          <t>506130</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>966957</t>
+          <t>966491</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1030778</t>
+          <t>1030810</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,74%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168549</t>
+          <t>168003</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>219665</t>
+          <t>216469</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261208</t>
+          <t>263548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>322265</t>
+          <t>320524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>450554</t>
+          <t>444815</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>525623</t>
+          <t>522716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>558918</t>
+          <t>562114</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610034</t>
+          <t>610580</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>503902</t>
+          <t>505643</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>564959</t>
+          <t>562619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1079127</t>
+          <t>1082034</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1154196</t>
+          <t>1159935</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,92%</t>
+          <t>72,28%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>730904</t>
+          <t>728195</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>829383</t>
+          <t>826325</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1172285</t>
+          <t>1179342</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1289757</t>
+          <t>1295341</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1937437</t>
+          <t>1929719</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2091778</t>
+          <t>2086393</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,07%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2564967</t>
+          <t>2568025</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2663446</t>
+          <t>2666155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2254785</t>
+          <t>2249201</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2372257</t>
+          <t>2365200</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4847114</t>
+          <t>4852499</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5001455</t>
+          <t>5009173</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>72,19%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido dos o más medicamentos en las dos últimas semanas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67208</t>
+          <t>66570</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100104</t>
+          <t>100729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95526</t>
+          <t>95732</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122494</t>
+          <t>122731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>169591</t>
+          <t>170043</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212614</t>
+          <t>212276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,32%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>211339</t>
+          <t>210714</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244235</t>
+          <t>244873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167141</t>
+          <t>166904</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194109</t>
+          <t>193903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388463</t>
+          <t>388801</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431486</t>
+          <t>431034</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>110977</t>
+          <t>108500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>154879</t>
+          <t>156441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178365</t>
+          <t>178811</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217891</t>
+          <t>217264</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>298999</t>
+          <t>301473</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>362841</t>
+          <t>360958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>363511</t>
+          <t>361949</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>407413</t>
+          <t>409890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297078</t>
+          <t>297705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336604</t>
+          <t>336158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>670518</t>
+          <t>672401</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>734360</t>
+          <t>731886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,83%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93251</t>
+          <t>95008</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126000</t>
+          <t>126872</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>135515</t>
+          <t>137495</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165815</t>
+          <t>166903</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238773</t>
+          <t>238012</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285019</t>
+          <t>281711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,35%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>190050</t>
+          <t>189178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>222799</t>
+          <t>221042</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>183313</t>
+          <t>182225</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>213613</t>
+          <t>211633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>52,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,18%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380159</t>
+          <t>383467</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>426405</t>
+          <t>427166</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88473</t>
+          <t>89624</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128583</t>
+          <t>128718</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,31%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>100755</t>
+          <t>104964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>219506</t>
+          <t>222529</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>207342</t>
+          <t>205354</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326607</t>
+          <t>325522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183974</t>
+          <t>183839</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>224084</t>
+          <t>222933</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,69%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256212</t>
+          <t>253189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>374963</t>
+          <t>370754</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>461667</t>
+          <t>462752</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>580932</t>
+          <t>582920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,95%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44631</t>
+          <t>43928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64596</t>
+          <t>63239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,17 +12104,17 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94188</t>
+          <t>94187</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49688</t>
+          <t>50069</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119712</t>
+          <t>119833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96539</t>
+          <t>104873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>170509</t>
+          <t>171795</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>39,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>114146</t>
+          <t>115503</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134111</t>
+          <t>134814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>64,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,17 +12217,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>164591</t>
+          <t>164592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>139067</t>
+          <t>138946</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>209091</t>
+          <t>208710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>267012</t>
+          <t>265726</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>340982</t>
+          <t>332648</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>76,03%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>87456</t>
+          <t>88482</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>116019</t>
+          <t>115150</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102344</t>
+          <t>102408</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>127401</t>
+          <t>128328</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196564</t>
+          <t>196906</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232849</t>
+          <t>233567</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,35%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>153617</t>
+          <t>154486</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>182180</t>
+          <t>181154</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>129655</t>
+          <t>128728</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>154648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>293843</t>
+          <t>293125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>330128</t>
+          <t>329786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,61%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>189580</t>
+          <t>190575</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245546</t>
+          <t>245918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367636</t>
+          <t>367504</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>656232</t>
+          <t>673809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>79,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>571654</t>
+          <t>570939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1005621</t>
+          <t>977098</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>66,31%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>378733</t>
+          <t>378361</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>434699</t>
+          <t>433704</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>193033</t>
+          <t>175456</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>481629</t>
+          <t>481761</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>56,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>467923</t>
+          <t>496446</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>901890</t>
+          <t>902605</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,25%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72591</t>
+          <t>73019</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>225377</t>
+          <t>227205</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>232157</t>
+          <t>234211</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277214</t>
+          <t>277385</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>258399</t>
+          <t>248424</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>496790</t>
+          <t>497521</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>703343</t>
+          <t>701515</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>856129</t>
+          <t>855701</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>440517</t>
+          <t>440346</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>485574</t>
+          <t>483520</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1149662</t>
+          <t>1148931</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1388053</t>
+          <t>1398028</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>769346</t>
+          <t>738827</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1057510</t>
+          <t>1054383</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1435776</t>
+          <t>1433857</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2015906</t>
+          <t>1977414</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2299674</t>
+          <t>2316995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3002654</t>
+          <t>2933743</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2402307</t>
+          <t>2405434</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2690471</t>
+          <t>2720990</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1696374</t>
+          <t>1734866</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2276504</t>
+          <t>2278423</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4169443</t>
+          <t>4238354</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4872423</t>
+          <t>4855102</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,13%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>67,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A_n_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A_n_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35510</t>
+          <t>34543</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60669</t>
+          <t>58765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55656</t>
+          <t>55241</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98029</t>
+          <t>98126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137170</t>
+          <t>135404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>212341</t>
+          <t>214245</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237500</t>
+          <t>238467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>175880</t>
+          <t>175844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>205182</t>
+          <t>205597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>396678</t>
+          <t>398444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>435819</t>
+          <t>435722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>54605</t>
+          <t>52891</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86071</t>
+          <t>85466</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134970</t>
+          <t>133870</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>176320</t>
+          <t>175217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>198194</t>
+          <t>198227</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250393</t>
+          <t>249071</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,98%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>407004</t>
+          <t>407609</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438470</t>
+          <t>440184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327629</t>
+          <t>328732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368979</t>
+          <t>370079</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,22%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>746631</t>
+          <t>747953</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>798830</t>
+          <t>798797</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40008</t>
+          <t>39380</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65998</t>
+          <t>64754</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73710</t>
+          <t>73631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105162</t>
+          <t>106356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118687</t>
+          <t>119016</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160042</t>
+          <t>162680</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,86%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>252848</t>
+          <t>254092</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278838</t>
+          <t>279466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230250</t>
+          <t>229056</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261702</t>
+          <t>261781</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>494216</t>
+          <t>491578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>535571</t>
+          <t>535242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52487</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81051</t>
+          <t>79888</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102388</t>
+          <t>103094</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>139040</t>
+          <t>138541</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>160448</t>
+          <t>162446</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>205978</t>
+          <t>206533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,29%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277620</t>
+          <t>278783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>306184</t>
+          <t>306750</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232416</t>
+          <t>232915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>269068</t>
+          <t>268362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>524149</t>
+          <t>523594</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569679</t>
+          <t>567681</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>77,75%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22002</t>
+          <t>22814</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>43206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59304</t>
+          <t>61731</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87821</t>
+          <t>88282</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87707</t>
+          <t>89519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123098</t>
+          <t>125235</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,47%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>160197</t>
+          <t>160102</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>181306</t>
+          <t>180494</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119847</t>
+          <t>119386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>148364</t>
+          <t>145937</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>287878</t>
+          <t>285741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>323269</t>
+          <t>321457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37873</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61517</t>
+          <t>63577</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67112</t>
+          <t>67169</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>96389</t>
+          <t>97359</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112202</t>
+          <t>110073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>150314</t>
+          <t>151871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>209294</t>
+          <t>207234</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>232938</t>
+          <t>232351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,28%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>181755</t>
+          <t>180785</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>211032</t>
+          <t>210975</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398641</t>
+          <t>397084</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>436753</t>
+          <t>438882</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,95%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89297</t>
+          <t>88644</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125541</t>
+          <t>126639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159228</t>
+          <t>157051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>204007</t>
+          <t>204093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>260314</t>
+          <t>260037</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>317865</t>
+          <t>318399</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>489486</t>
+          <t>488388</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>525730</t>
+          <t>526383</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>434212</t>
+          <t>434126</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>478991</t>
+          <t>481168</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>935381</t>
+          <t>934847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>992932</t>
+          <t>993209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>74,59%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>133282</t>
+          <t>133529</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177286</t>
+          <t>177580</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>210750</t>
+          <t>211756</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>261217</t>
+          <t>263865</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>359280</t>
+          <t>359293</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>426686</t>
+          <t>428864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>566509</t>
+          <t>566215</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610513</t>
+          <t>610266</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>522294</t>
+          <t>519646</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>572761</t>
+          <t>571755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1100620</t>
+          <t>1098442</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1168026</t>
+          <t>1168013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,06%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>528764</t>
+          <t>531817</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>612259</t>
+          <t>613638</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>957519</t>
+          <t>956577</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1062880</t>
+          <t>1067183</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1508901</t>
+          <t>1507175</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1646994</t>
+          <t>1650446</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2664284</t>
+          <t>2662905</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2747779</t>
+          <t>2744726</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2316317</t>
+          <t>2312014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2421678</t>
+          <t>2422620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>68,55%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5008747</t>
+          <t>5005295</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5146840</t>
+          <t>5148566</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57710</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88762</t>
+          <t>89906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>102530</t>
+          <t>101457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138057</t>
+          <t>136365</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,06%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170189</t>
+          <t>166265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>216288</t>
+          <t>216446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,19%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>205976</t>
+          <t>204832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>237028</t>
+          <t>237352</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>149188</t>
+          <t>150880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>184715</t>
+          <t>185788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>52,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>365695</t>
+          <t>365537</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>411794</t>
+          <t>415718</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,43%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112439</t>
+          <t>111102</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>153868</t>
+          <t>152768</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195487</t>
+          <t>196262</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>243780</t>
+          <t>242820</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,54%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>318099</t>
+          <t>318210</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>383251</t>
+          <t>383698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,28%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351659</t>
+          <t>352759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393088</t>
+          <t>394425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>279985</t>
+          <t>280945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>328278</t>
+          <t>327503</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>646041</t>
+          <t>645594</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>711193</t>
+          <t>711082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79695</t>
+          <t>80858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>113806</t>
+          <t>115145</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131386</t>
+          <t>130952</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>168859</t>
+          <t>168365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221309</t>
+          <t>221953</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273219</t>
+          <t>272096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,91%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210240</t>
+          <t>208901</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>244351</t>
+          <t>243188</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172161</t>
+          <t>172655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>209634</t>
+          <t>210068</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>61,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>391847</t>
+          <t>392970</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>443757</t>
+          <t>443113</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,63%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74759</t>
+          <t>74636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110778</t>
+          <t>109490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156856</t>
+          <t>156768</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>195268</t>
+          <t>195926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>243474</t>
+          <t>242917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>297448</t>
+          <t>295263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263204</t>
+          <t>264492</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>299223</t>
+          <t>299346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,01%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193683</t>
+          <t>193025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>232095</t>
+          <t>232183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>465485</t>
+          <t>467670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519459</t>
+          <t>520016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,16%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46484</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73341</t>
+          <t>73946</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,49%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103758</t>
+          <t>103608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>133287</t>
+          <t>132166</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>156469</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196858</t>
+          <t>196880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>139277</t>
+          <t>138672</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>166134</t>
+          <t>166879</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86304</t>
+          <t>87425</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>115833</t>
+          <t>115983</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,75%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235351</t>
+          <t>235329</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275740</t>
+          <t>276421</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,96%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73833</t>
+          <t>75018</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>105655</t>
+          <t>105815</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106444</t>
+          <t>106816</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>140625</t>
+          <t>140068</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>190139</t>
+          <t>187339</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234525</t>
+          <t>233862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,21%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>168326</t>
+          <t>168166</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200148</t>
+          <t>198963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>139406</t>
+          <t>139963</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173587</t>
+          <t>173215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>319487</t>
+          <t>320150</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>363873</t>
+          <t>366673</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>57,67%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>135533</t>
+          <t>140477</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>183807</t>
+          <t>184711</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>238438</t>
+          <t>237146</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287912</t>
+          <t>289025</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>388431</t>
+          <t>391921</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459692</t>
+          <t>461767</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>478981</t>
+          <t>478077</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>527255</t>
+          <t>522311</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>405941</t>
+          <t>404828</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>455415</t>
+          <t>456707</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,64%</t>
+          <t>65,82%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>896949</t>
+          <t>894874</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>968210</t>
+          <t>964720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142913</t>
+          <t>139865</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>188713</t>
+          <t>188206</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,82 +6472,82 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>24,16%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>257173</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>228807</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>283939</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>31,22%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>27,77%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>34,46%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>384</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>421798</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>388198</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>457614</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>26,31%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>24,22%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>257173</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>284878</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>34,58%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>384</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>421798</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>384904</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>459734</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>26,31%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>590385</t>
+          <t>590892</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>636185</t>
+          <t>639233</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,82 +6585,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>75,84%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>82,05%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>566680</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>539914</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>595046</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>68,78%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>65,54%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>72,23%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>1090</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>1181153</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1145337</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>1214753</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>73,69%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>71,45%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>75,78%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>81,66%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>520</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>566680</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>538975</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>594540</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>65,42%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>72,17%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>1181153</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>1143217</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>1218047</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>73,69%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>71,32%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>813379</t>
+          <t>809215</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>919139</t>
+          <t>914675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1364502</t>
+          <t>1369206</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1482274</t>
+          <t>1483275</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,68%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2212676</t>
+          <t>2210844</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2370765</t>
+          <t>2366137</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,87%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2507640</t>
+          <t>2512104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2613400</t>
+          <t>2617564</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2076035</t>
+          <t>2075034</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2193807</t>
+          <t>2189103</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4614323</t>
+          <t>4618951</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4772412</t>
+          <t>4774244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,35%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41986</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68530</t>
+          <t>69226</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73947</t>
+          <t>73285</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105579</t>
+          <t>106889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>124322</t>
+          <t>125657</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165007</t>
+          <t>167341</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225231</t>
+          <t>224535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>252347</t>
+          <t>251775</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183124</t>
+          <t>181814</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>214756</t>
+          <t>215418</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,39%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>417457</t>
+          <t>415123</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>458142</t>
+          <t>456807</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,43%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>98304</t>
+          <t>96678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>136170</t>
+          <t>133525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174659</t>
+          <t>173807</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219201</t>
+          <t>219387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>281382</t>
+          <t>280219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>339341</t>
+          <t>343492</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366405</t>
+          <t>369050</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>404271</t>
+          <t>405897</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303883</t>
+          <t>303697</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>348425</t>
+          <t>349277</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686318</t>
+          <t>682167</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>744277</t>
+          <t>745440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>86092</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>80889</t>
+          <t>81183</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114700</t>
+          <t>116749</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146744</t>
+          <t>144732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190489</t>
+          <t>190659</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>234501</t>
+          <t>232473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>262717</t>
+          <t>261315</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221609</t>
+          <t>219560</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255420</t>
+          <t>255126</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,89%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464385</t>
+          <t>464215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>508130</t>
+          <t>510142</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,9%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>92431</t>
+          <t>94132</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>130630</t>
+          <t>130652</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,7 +8423,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150219</t>
+          <t>151746</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190666</t>
+          <t>191534</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>253861</t>
+          <t>253551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312351</t>
+          <t>308578</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>239334</t>
+          <t>239312</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>277533</t>
+          <t>275832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196617</t>
+          <t>195749</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>237064</t>
+          <t>235537</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>444896</t>
+          <t>448669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>503386</t>
+          <t>503696</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,52%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>30017</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>53746</t>
+          <t>53394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83667</t>
+          <t>82937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113156</t>
+          <t>112640</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120138</t>
+          <t>122194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158384</t>
+          <t>158883</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,97%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157475</t>
+          <t>157827</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>180879</t>
+          <t>181204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>105431</t>
+          <t>105947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134920</t>
+          <t>135650</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,23%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>271424</t>
+          <t>270925</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>309670</t>
+          <t>307614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,57%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41345</t>
+          <t>43232</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68746</t>
+          <t>70345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>69585</t>
+          <t>66824</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98562</t>
+          <t>97790</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>119284</t>
+          <t>119212</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>160514</t>
+          <t>161199</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>194377</t>
+          <t>192778</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>221778</t>
+          <t>219891</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>174553</t>
+          <t>175325</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>203530</t>
+          <t>206291</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>375724</t>
+          <t>375039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416954</t>
+          <t>417026</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,77%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>117014</t>
+          <t>118106</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>160210</t>
+          <t>162613</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185164</t>
+          <t>183232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232918</t>
+          <t>234349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>317042</t>
+          <t>313907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>381361</t>
+          <t>379122</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>496348</t>
+          <t>493945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>539544</t>
+          <t>538452</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>458376</t>
+          <t>456945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>506130</t>
+          <t>508062</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>966491</t>
+          <t>968730</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1030810</t>
+          <t>1033945</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,71%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>168003</t>
+          <t>168725</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>216469</t>
+          <t>217578</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>263548</t>
+          <t>264252</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>320524</t>
+          <t>322603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>444815</t>
+          <t>447206</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>522716</t>
+          <t>518764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,33%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>562114</t>
+          <t>561005</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610580</t>
+          <t>609858</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>505643</t>
+          <t>503564</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>562619</t>
+          <t>561915</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1082034</t>
+          <t>1085986</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1159935</t>
+          <t>1157544</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,13%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>728195</t>
+          <t>731051</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>826325</t>
+          <t>828740</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1179342</t>
+          <t>1177292</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1295341</t>
+          <t>1295952</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1929719</t>
+          <t>1938917</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2086393</t>
+          <t>2087176</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,08%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2568025</t>
+          <t>2565610</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2666155</t>
+          <t>2663299</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2249201</t>
+          <t>2248590</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2365200</t>
+          <t>2367250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4852499</t>
+          <t>4851716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5009173</t>
+          <t>4999975</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,06%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>82468</t>
+          <t>84889</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66570</t>
+          <t>70046</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>99372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>108718</t>
+          <t>114600</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>95732</t>
+          <t>99453</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122731</t>
+          <t>127590</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>191186</t>
+          <t>199489</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>170043</t>
+          <t>180782</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212276</t>
+          <t>220904</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>228975</t>
+          <t>233956</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>210714</t>
+          <t>219473</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>244873</t>
+          <t>248799</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,52%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>180917</t>
+          <t>201461</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>166904</t>
+          <t>188471</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>193903</t>
+          <t>216608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>409891</t>
+          <t>435417</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>388801</t>
+          <t>414002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>431034</t>
+          <t>454124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,58%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,53%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>131166</t>
+          <t>135068</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>108500</t>
+          <t>113323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156441</t>
+          <t>158552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,67 +11075,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>198962</t>
+          <t>207709</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>178811</t>
+          <t>188076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>217264</t>
+          <t>227023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>34,42%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>41,54%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>342777</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>315512</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>373941</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>29,29%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>34,72%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>42,19%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>330128</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>301473</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>360958</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>31,95%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>29,17%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>387224</t>
+          <t>395579</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>361949</t>
+          <t>372095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>409890</t>
+          <t>417324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,67 +11188,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>316007</t>
+          <t>338785</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>297705</t>
+          <t>319471</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>336158</t>
+          <t>358418</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>58,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>65,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>734364</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>703200</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>761629</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>68,18%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>65,28%</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>675</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>703231</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>672401</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>731886</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>68,05%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,83%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514969</t>
+          <t>546494</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1033359</t>
+          <t>1077141</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>109560</t>
+          <t>112222</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95008</t>
+          <t>96615</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>126872</t>
+          <t>130280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>151412</t>
+          <t>155550</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>137495</t>
+          <t>138939</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>166903</t>
+          <t>170917</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>260972</t>
+          <t>267772</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238012</t>
+          <t>246189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281711</t>
+          <t>290359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>206490</t>
+          <t>203771</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189178</t>
+          <t>185713</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>221042</t>
+          <t>219378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>197716</t>
+          <t>200831</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182225</t>
+          <t>185464</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>211633</t>
+          <t>217442</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>404206</t>
+          <t>404603</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>383467</t>
+          <t>382016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>427166</t>
+          <t>426186</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>107585</t>
+          <t>121891</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>89624</t>
+          <t>100773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128718</t>
+          <t>145397</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>173824</t>
+          <t>190827</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104964</t>
+          <t>171969</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>222529</t>
+          <t>212281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>281409</t>
+          <t>312718</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>205354</t>
+          <t>283812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>325522</t>
+          <t>342998</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,3%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>204972</t>
+          <t>251254</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>183839</t>
+          <t>227748</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222933</t>
+          <t>272372</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>301894</t>
+          <t>231134</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>253189</t>
+          <t>209680</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>370754</t>
+          <t>249992</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>506865</t>
+          <t>482389</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>462752</t>
+          <t>452109</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>582920</t>
+          <t>511295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>64,31%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>56941</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43928</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63239</t>
+          <t>67129</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>94187</t>
+          <t>97546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>50069</t>
+          <t>86386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>119833</t>
+          <t>107956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>37,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147257</t>
+          <t>154487</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104873</t>
+          <t>140387</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>171795</t>
+          <t>171800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>39,53%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>125673</t>
+          <t>148724</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>115503</t>
+          <t>138536</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134814</t>
+          <t>159518</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>67,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,42%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>164592</t>
+          <t>131372</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>138946</t>
+          <t>120962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208710</t>
+          <t>142532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>290264</t>
+          <t>280095</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>265726</t>
+          <t>262782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>332648</t>
+          <t>294195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>67,7%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>258779</t>
+          <t>228918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>437521</t>
+          <t>434582</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>101237</t>
+          <t>99329</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>88482</t>
+          <t>85669</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>115150</t>
+          <t>113477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>113839</t>
+          <t>117137</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>102408</t>
+          <t>103946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>128328</t>
+          <t>129614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>215077</t>
+          <t>216466</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>196906</t>
+          <t>197854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>233567</t>
+          <t>235544</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>168399</t>
+          <t>171378</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>154486</t>
+          <t>157230</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>181154</t>
+          <t>185038</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>68,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>143217</t>
+          <t>146613</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>128728</t>
+          <t>134136</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154648</t>
+          <t>159804</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>311615</t>
+          <t>317991</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>293125</t>
+          <t>298913</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>329786</t>
+          <t>336603</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>216851</t>
+          <t>258063</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>190575</t>
+          <t>227578</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245918</t>
+          <t>286684</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>490951</t>
+          <t>342298</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>367504</t>
+          <t>316400</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>673809</t>
+          <t>368038</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>707801</t>
+          <t>600362</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>570939</t>
+          <t>559473</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>977098</t>
+          <t>641417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>48,03%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>43,0%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>407428</t>
+          <t>461624</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>378361</t>
+          <t>433003</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>433704</t>
+          <t>492109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>358314</t>
+          <t>429759</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>175456</t>
+          <t>404019</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>481761</t>
+          <t>455657</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>765743</t>
+          <t>891382</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>496446</t>
+          <t>850327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>902605</t>
+          <t>932271</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>159395</t>
+          <t>178161</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73019</t>
+          <t>156655</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227205</t>
+          <t>202669</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>254775</t>
+          <t>285657</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>234211</t>
+          <t>260762</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>277385</t>
+          <t>309205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>414170</t>
+          <t>463818</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248424</t>
+          <t>429896</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>497521</t>
+          <t>500418</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>769325</t>
+          <t>619911</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>701515</t>
+          <t>595403</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>855701</t>
+          <t>641417</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>462956</t>
+          <t>545674</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>440346</t>
+          <t>522126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>483520</t>
+          <t>570569</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,64%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1232282</t>
+          <t>1165585</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1148931</t>
+          <t>1128985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1398028</t>
+          <t>1199507</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>961331</t>
+          <t>1046564</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>738827</t>
+          <t>991785</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1054383</t>
+          <t>1110818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1586668</t>
+          <t>1511326</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1433857</t>
+          <t>1459245</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1977414</t>
+          <t>1566536</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2547999</t>
+          <t>2557890</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2316995</t>
+          <t>2475849</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2933743</t>
+          <t>2636790</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2498486</t>
+          <t>2486198</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2405434</t>
+          <t>2421944</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2720990</t>
+          <t>2540977</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2125612</t>
+          <t>2225628</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1734866</t>
+          <t>2170418</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2278423</t>
+          <t>2277709</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4624098</t>
+          <t>4711826</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4238354</t>
+          <t>4632926</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4855102</t>
+          <t>4793867</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
